--- a/artfynd/A 18894-2023 artfynd.xlsx
+++ b/artfynd/A 18894-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18894-2023 artfynd.xlsx
+++ b/artfynd/A 18894-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83185947</v>
+        <v>83185928</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507103.3087603191</v>
+        <v>507041</v>
       </c>
       <c r="R2" t="n">
-        <v>6491138.590988014</v>
+        <v>6491138</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>EC7E6BB9-5381-4BE7-B350-D935E377B475</t>
+          <t>E877D7A7-0BE8-428B-9512-8D8C36EE2A87</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,19 +752,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83185948</v>
+        <v>83185936</v>
       </c>
       <c r="B3" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507148.1364366793</v>
+        <v>507090</v>
       </c>
       <c r="R3" t="n">
-        <v>6491204.928933419</v>
+        <v>6491191</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,7 +854,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>10753106-6930-43FD-B172-E20899AD765E</t>
+          <t>8D6EEF1A-E30F-4A56-AC79-C11AEADF319D</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -882,19 +862,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83185928</v>
+        <v>83185937</v>
       </c>
       <c r="B4" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507041.112036276</v>
+        <v>507097</v>
       </c>
       <c r="R4" t="n">
-        <v>6491138.478409418</v>
+        <v>6491199</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -999,7 +964,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>E877D7A7-0BE8-428B-9512-8D8C36EE2A87</t>
+          <t>BE169413-7A67-4770-A714-749CEC034AB4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,19 +972,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83185936</v>
+        <v>83185938</v>
       </c>
       <c r="B5" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507089.6239494531</v>
+        <v>507101</v>
       </c>
       <c r="R5" t="n">
-        <v>6491191.258154005</v>
+        <v>6491207</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1124,7 +1074,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>8D6EEF1A-E30F-4A56-AC79-C11AEADF319D</t>
+          <t>1B9599F0-DD7A-48C9-BB59-6E600784F63F</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,19 +1082,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83185938</v>
+        <v>83185940</v>
       </c>
       <c r="B6" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507101.0929550247</v>
+        <v>507107</v>
       </c>
       <c r="R6" t="n">
-        <v>6491207.451638348</v>
+        <v>6491214</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1249,7 +1184,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1B9599F0-DD7A-48C9-BB59-6E600784F63F</t>
+          <t>74FCBA24-8306-49C9-9294-1552ED8FCCAB</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1257,19 +1192,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83185946</v>
+        <v>83185944</v>
       </c>
       <c r="B7" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507128.9172720168</v>
+        <v>507151</v>
       </c>
       <c r="R7" t="n">
-        <v>6491139.681041459</v>
+        <v>6491128</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1374,7 +1294,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>B4813B41-5A78-435F-BEBD-0994FC4A9376</t>
+          <t>3109217E-94A0-4507-9D7F-1C4047BAC152</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1382,19 +1302,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83185950</v>
+        <v>83185946</v>
       </c>
       <c r="B8" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507184.2119413285</v>
+        <v>507129</v>
       </c>
       <c r="R8" t="n">
-        <v>6491198.213022097</v>
+        <v>6491140</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1499,7 +1404,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>E1581A6E-1118-4E9D-BE86-DBF5F8921242</t>
+          <t>B4813B41-5A78-435F-BEBD-0994FC4A9376</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1507,19 +1412,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,15 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83185937</v>
+        <v>83185947</v>
       </c>
       <c r="B9" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507097.4495516249</v>
+        <v>507103</v>
       </c>
       <c r="R9" t="n">
-        <v>6491199.09784897</v>
+        <v>6491139</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1624,7 +1514,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>BE169413-7A67-4770-A714-749CEC034AB4</t>
+          <t>EC7E6BB9-5381-4BE7-B350-D935E377B475</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1632,19 +1522,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,15 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>83185940</v>
+        <v>83185950</v>
       </c>
       <c r="B10" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507107.3524458918</v>
+        <v>507184</v>
       </c>
       <c r="R10" t="n">
-        <v>6491214.245081838</v>
+        <v>6491198</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1749,7 +1624,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>74FCBA24-8306-49C9-9294-1552ED8FCCAB</t>
+          <t>E1581A6E-1118-4E9D-BE86-DBF5F8921242</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1757,19 +1632,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1803,12 +1668,7 @@
         <v>83185951</v>
       </c>
       <c r="B11" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507190.4799437877</v>
+        <v>507190</v>
       </c>
       <c r="R11" t="n">
-        <v>6491200.311347042</v>
+        <v>6491200</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1882,19 +1742,9 @@
           <t>2003-02-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2003-02-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,6 +1768,116 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>83185948</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Birgittas udde, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>507148</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6491205</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ekebyborna</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>10753106-6930-43FD-B172-E20899AD765E</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2003-02-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2003-02-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
